--- a/artfynd/A 23638-2023 artfynd.xlsx
+++ b/artfynd/A 23638-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23638-2023 artfynd.xlsx
+++ b/artfynd/A 23638-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110060421</v>
+        <v>110060428</v>
       </c>
       <c r="B2" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattland, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411208.7703994368</v>
+        <v>411291</v>
       </c>
       <c r="R2" t="n">
-        <v>7025279.743498789</v>
+        <v>7025371</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +743,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110060422</v>
+        <v>110060415</v>
       </c>
       <c r="B3" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411620.93420139</v>
+        <v>411290</v>
       </c>
       <c r="R3" t="n">
-        <v>7025267.012757186</v>
+        <v>7025264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,24 +844,14 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110060427</v>
+        <v>110060417</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +889,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brattland, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411409.7740157063</v>
+        <v>411284</v>
       </c>
       <c r="R4" t="n">
-        <v>7025032.483387623</v>
+        <v>7025289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +950,14 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110060417</v>
+        <v>110060418</v>
       </c>
       <c r="B5" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411283.6994215957</v>
+        <v>411272</v>
       </c>
       <c r="R5" t="n">
-        <v>7025288.901280839</v>
+        <v>7025308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,24 +1056,14 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,15 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110060420</v>
+        <v>110060419</v>
       </c>
       <c r="B6" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411272.1662275246</v>
+        <v>411283</v>
       </c>
       <c r="R6" t="n">
-        <v>7025343.578228693</v>
+        <v>7025314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,24 +1162,14 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,15 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110060415</v>
+        <v>110060420</v>
       </c>
       <c r="B7" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411290.2087285602</v>
+        <v>411272</v>
       </c>
       <c r="R7" t="n">
-        <v>7025264.01279831</v>
+        <v>7025343</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,19 +1268,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1392,15 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110060425</v>
+        <v>110060421</v>
       </c>
       <c r="B8" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411500.4353926617</v>
+        <v>411209</v>
       </c>
       <c r="R8" t="n">
-        <v>7025236.641728432</v>
+        <v>7025280</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,19 +1374,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1513,15 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110060419</v>
+        <v>110060422</v>
       </c>
       <c r="B9" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411283.4832894632</v>
+        <v>411621</v>
       </c>
       <c r="R9" t="n">
-        <v>7025313.615521053</v>
+        <v>7025267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,19 +1480,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1634,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110060428</v>
+        <v>110060424</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,34 +1525,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brattland, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411290.9159910702</v>
+        <v>411560</v>
       </c>
       <c r="R10" t="n">
-        <v>7025370.912074795</v>
+        <v>7025290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,19 +1586,14 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,6 +1617,112 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110060425</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brattland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411500</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7025236</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23638-2023 artfynd.xlsx
+++ b/artfynd/A 23638-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060428</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060417</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060418</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060419</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060420</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060421</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060422</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060424</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,8 +1773,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110060425</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>